--- a/results/03-2025/beta/inputs-03-2025.xlsx
+++ b/results/03-2025/beta/inputs-03-2025.xlsx
@@ -35387,28 +35387,28 @@
         <v>-1</v>
       </c>
       <c r="D221" t="n">
-        <v>0.00672681736450054</v>
+        <v>0.00659838171076288</v>
       </c>
       <c r="E221" t="n">
-        <v>0.00486028642658831</v>
+        <v>0.00473445376829473</v>
       </c>
       <c r="F221" t="n">
-        <v>0.0036140919964156</v>
+        <v>0.00317714234930788</v>
       </c>
       <c r="G221" t="n">
-        <v>0.00460786450387629</v>
+        <v>0.00442105918615154</v>
       </c>
       <c r="H221" t="n">
-        <v>0.00593953792819213</v>
+        <v>0.00590721391225646</v>
       </c>
       <c r="I221" t="n">
         <v>0.00574380039423361</v>
       </c>
       <c r="J221" t="n">
-        <v>29719.6</v>
+        <v>29723.9</v>
       </c>
       <c r="K221" t="n">
-        <v>20262.7</v>
+        <v>20255.5</v>
       </c>
       <c r="L221" t="n">
         <v>1924.7</v>
@@ -35420,25 +35420,25 @@
         <v>79.275</v>
       </c>
       <c r="O221" t="n">
-        <v>3173.3</v>
+        <v>3175</v>
       </c>
       <c r="P221" t="n">
-        <v>4515.2</v>
+        <v>4514.4</v>
       </c>
       <c r="Q221" t="n">
-        <v>2515.7</v>
+        <v>2519.8</v>
       </c>
       <c r="R221" t="n">
-        <v>509.332755158353</v>
+        <v>512.1</v>
       </c>
       <c r="S221" t="n">
         <v>71.1791672183253</v>
       </c>
       <c r="T221" t="n">
-        <v>163.324749650848</v>
+        <v>164.2</v>
       </c>
       <c r="U221" t="n">
-        <v>2171.498</v>
+        <v>2169.998</v>
       </c>
       <c r="V221" t="n">
         <v>217.7</v>
@@ -35477,22 +35477,22 @@
         <v>1773.675</v>
       </c>
       <c r="AH221" t="n">
-        <v>302.425</v>
+        <v>289.625</v>
       </c>
       <c r="AI221" t="n">
-        <v>-2622.366</v>
+        <v>-2622.27</v>
       </c>
       <c r="AJ221" t="n">
-        <v>-1449.522</v>
+        <v>-1450.014</v>
       </c>
       <c r="AK221" t="n">
-        <v>-178.064425171945</v>
+        <v>-178.156666666666</v>
       </c>
       <c r="AL221" t="n">
-        <v>-65.4641583216949</v>
+        <v>-65.4933333333333</v>
       </c>
       <c r="AM221" t="n">
-        <v>1928.338875</v>
+        <v>1928.001375</v>
       </c>
       <c r="AN221" t="n">
         <v>193.545</v>
@@ -35528,7 +35528,7 @@
         <v>1545.3666</v>
       </c>
       <c r="AY221" t="n">
-        <v>264.6459</v>
+        <v>261.7659</v>
       </c>
     </row>
     <row r="222">
@@ -35554,16 +35554,16 @@
         <v>0.0075994791260281</v>
       </c>
       <c r="H222" t="n">
-        <v>0.00620657034618466</v>
+        <v>0.0086516660980791</v>
       </c>
       <c r="I222" t="n">
         <v>0.00562014078474316</v>
       </c>
       <c r="J222" t="n">
-        <v>30035.5315204789</v>
+        <v>30039.8772312401</v>
       </c>
       <c r="K222" t="n">
-        <v>20480.929290042</v>
+        <v>20473.651746038</v>
       </c>
       <c r="L222" t="n">
         <v>1918.51028958294</v>
@@ -35575,25 +35575,25 @@
         <v>79.275</v>
       </c>
       <c r="O222" t="n">
-        <v>3203.38856116179</v>
+        <v>3205.10468020316</v>
       </c>
       <c r="P222" t="n">
-        <v>4578.84278494077</v>
+        <v>4561.53819531556</v>
       </c>
       <c r="Q222" t="n">
-        <v>2532.0824781373</v>
+        <v>2537.46159402043</v>
       </c>
       <c r="R222" t="n">
-        <v>526.099889428512</v>
+        <v>528.958231426876</v>
       </c>
       <c r="S222" t="n">
         <v>73.9806362924226</v>
       </c>
       <c r="T222" t="n">
-        <v>163.759599441357</v>
+        <v>159.562778829061</v>
       </c>
       <c r="U222" t="n">
-        <v>2215.99639375</v>
+        <v>2214.4883475</v>
       </c>
       <c r="V222" t="n">
         <v>228.029047409692</v>
@@ -35629,25 +35629,25 @@
         <v>0</v>
       </c>
       <c r="AG222" t="n">
-        <v>1828.47693961422</v>
+        <v>1827.44055330551</v>
       </c>
       <c r="AH222" t="n">
-        <v>314.374441798612</v>
+        <v>310.542533565974</v>
       </c>
       <c r="AI222" t="n">
-        <v>-2652.60513419289</v>
+        <v>-2650.43258343787</v>
       </c>
       <c r="AJ222" t="n">
-        <v>-1466.92589737648</v>
+        <v>-1468.06339128245</v>
       </c>
       <c r="AK222" t="n">
-        <v>-182.947754819562</v>
+        <v>-183.135274380896</v>
       </c>
       <c r="AL222" t="n">
-        <v>-65.2294783030734</v>
+        <v>-65.118759294302</v>
       </c>
       <c r="AM222" t="n">
-        <v>1951.89578859375</v>
+        <v>1951.2189781875</v>
       </c>
       <c r="AN222" t="n">
         <v>197.894035667181</v>
@@ -35680,10 +35680,10 @@
         <v>0.35145</v>
       </c>
       <c r="AX222" t="n">
-        <v>1581.4903364132</v>
+        <v>1581.25714949374</v>
       </c>
       <c r="AY222" t="n">
-        <v>271.013724404688</v>
+        <v>267.271545052344</v>
       </c>
     </row>
     <row r="223">
@@ -35709,16 +35709,16 @@
         <v>0.00707611529348728</v>
       </c>
       <c r="H223" t="n">
-        <v>0.00557412911254063</v>
+        <v>0.00631091568942632</v>
       </c>
       <c r="I223" t="n">
         <v>0.00571780133544419</v>
       </c>
       <c r="J223" t="n">
-        <v>30344.9520869847</v>
+        <v>30349.3425664653</v>
       </c>
       <c r="K223" t="n">
-        <v>20720.9413565049</v>
+        <v>20713.5785283641</v>
       </c>
       <c r="L223" t="n">
         <v>1918.21157840012</v>
@@ -35730,25 +35730,25 @@
         <v>75.203</v>
       </c>
       <c r="O223" t="n">
-        <v>3229.63630260393</v>
+        <v>3231.36648308306</v>
       </c>
       <c r="P223" t="n">
-        <v>4601.87789173116</v>
+        <v>4584.48435128978</v>
       </c>
       <c r="Q223" t="n">
-        <v>2563.56513203677</v>
+        <v>2569.02647794275</v>
       </c>
       <c r="R223" t="n">
-        <v>543.418994465887</v>
+        <v>546.371432521478</v>
       </c>
       <c r="S223" t="n">
         <v>88.3944428040623</v>
       </c>
       <c r="T223" t="n">
-        <v>163.691956140612</v>
+        <v>159.49686908653</v>
       </c>
       <c r="U223" t="n">
-        <v>2222.69639375</v>
+        <v>2221.1883475</v>
       </c>
       <c r="V223" t="n">
         <v>231.362463474923</v>
@@ -35784,25 +35784,25 @@
         <v>0</v>
       </c>
       <c r="AG223" t="n">
-        <v>1856.9365023439</v>
+        <v>1855.88327500081</v>
       </c>
       <c r="AH223" t="n">
-        <v>320.795107851913</v>
+        <v>316.035339118237</v>
       </c>
       <c r="AI223" t="n">
-        <v>-2681.16848120063</v>
+        <v>-2676.95670559264</v>
       </c>
       <c r="AJ223" t="n">
-        <v>-1484.92171322089</v>
+        <v>-1486.46856863558</v>
       </c>
       <c r="AK223" t="n">
-        <v>-187.158387968425</v>
+        <v>-187.444322131612</v>
       </c>
       <c r="AL223" t="n">
-        <v>-65.4325435077605</v>
+        <v>-65.181988263853</v>
       </c>
       <c r="AM223" t="n">
-        <v>1971.5377021875</v>
+        <v>1970.521581375</v>
       </c>
       <c r="AN223" t="n">
         <v>202.205589949038</v>
@@ -35835,10 +35835,10 @@
         <v>0.250425</v>
       </c>
       <c r="AX223" t="n">
-        <v>1617.86822444058</v>
+        <v>1617.39806136892</v>
       </c>
       <c r="AY223" t="n">
-        <v>276.470448671368</v>
+        <v>271.657321353947</v>
       </c>
     </row>
     <row r="224">
@@ -35864,16 +35864,16 @@
         <v>0.00774551207611962</v>
       </c>
       <c r="H224" t="n">
-        <v>0.00542443641023826</v>
+        <v>0.00591602658436119</v>
       </c>
       <c r="I224" t="n">
         <v>0.00573662843673683</v>
       </c>
       <c r="J224" t="n">
-        <v>30647.661362472</v>
+        <v>30652.0956396446</v>
       </c>
       <c r="K224" t="n">
-        <v>20926.3218199022</v>
+        <v>20918.8860133659</v>
       </c>
       <c r="L224" t="n">
         <v>1923.76937281071</v>
@@ -35885,25 +35885,25 @@
         <v>75.203</v>
       </c>
       <c r="O224" t="n">
-        <v>3259.15180098305</v>
+        <v>3260.8977935024</v>
       </c>
       <c r="P224" t="n">
-        <v>4625.12586957864</v>
+        <v>4607.64296759388</v>
       </c>
       <c r="Q224" t="n">
-        <v>2590.60267019395</v>
+        <v>2596.13498000776</v>
       </c>
       <c r="R224" t="n">
-        <v>561.308241039732</v>
+        <v>564.357872776274</v>
       </c>
       <c r="S224" t="n">
         <v>103.083510693309</v>
       </c>
       <c r="T224" t="n">
-        <v>163.832074406442</v>
+        <v>159.633396410345</v>
       </c>
       <c r="U224" t="n">
-        <v>2229.39639375</v>
+        <v>2227.8883475</v>
       </c>
       <c r="V224" t="n">
         <v>234.744608694576</v>
@@ -35939,25 +35939,25 @@
         <v>0</v>
       </c>
       <c r="AG224" t="n">
-        <v>1887.0287015469</v>
+        <v>1886.09917606882</v>
       </c>
       <c r="AH224" t="n">
-        <v>326.181972475158</v>
+        <v>320.318054371515</v>
       </c>
       <c r="AI224" t="n">
-        <v>-2706.41101845362</v>
+        <v>-2701.13956998497</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-1502.82708495593</v>
+        <v>-1504.71507059529</v>
       </c>
       <c r="AK224" t="n">
-        <v>-192.461996003083</v>
+        <v>-192.849584557487</v>
       </c>
       <c r="AL224" t="n">
-        <v>-65.5902793213086</v>
+        <v>-65.1997681441978</v>
       </c>
       <c r="AM224" t="n">
-        <v>1988.90711578125</v>
+        <v>1987.5516845625</v>
       </c>
       <c r="AN224" t="n">
         <v>205.163126905318</v>
@@ -35990,10 +35990,10 @@
         <v>0.222075</v>
       </c>
       <c r="AX224" t="n">
-        <v>1652.87635728863</v>
+        <v>1652.19705098441</v>
       </c>
       <c r="AY224" t="n">
-        <v>284.349717478279</v>
+        <v>278.217208587538</v>
       </c>
     </row>
     <row r="225">
@@ -36025,10 +36025,10 @@
         <v>0.00571666765914358</v>
       </c>
       <c r="J225" t="n">
-        <v>30941.3554709197</v>
+        <v>30945.8322414188</v>
       </c>
       <c r="K225" t="n">
-        <v>21124.5751997701</v>
+        <v>21117.0689473241</v>
       </c>
       <c r="L225" t="n">
         <v>1929.56732068516</v>
@@ -36040,25 +36040,25 @@
         <v>75.203</v>
       </c>
       <c r="O225" t="n">
-        <v>3289.76921801178</v>
+        <v>3291.53161289113</v>
       </c>
       <c r="P225" t="n">
-        <v>4648.58683405003</v>
+        <v>4631.01415707285</v>
       </c>
       <c r="Q225" t="n">
-        <v>2617.237284825</v>
+        <v>2622.84419265443</v>
       </c>
       <c r="R225" t="n">
-        <v>557.839987860135</v>
+        <v>560.870776304892</v>
       </c>
       <c r="S225" t="n">
         <v>109.658761987664</v>
       </c>
       <c r="T225" t="n">
-        <v>163.749936112679</v>
+        <v>159.553363151557</v>
       </c>
       <c r="U225" t="n">
-        <v>2219.85739375</v>
+        <v>2218.3493475</v>
       </c>
       <c r="V225" t="n">
         <v>238.176195410118</v>
@@ -36094,25 +36094,25 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>1914.20570616006</v>
+        <v>1913.63552852275</v>
       </c>
       <c r="AH225" t="n">
-        <v>331.675488007072</v>
+        <v>324.516573895782</v>
       </c>
       <c r="AI225" t="n">
-        <v>-2730.86676503576</v>
+        <v>-2724.53020775633</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-1520.32965121272</v>
+        <v>-1522.56278503725</v>
       </c>
       <c r="AK225" t="n">
-        <v>-197.493328931754</v>
+        <v>-197.98194376765</v>
       </c>
       <c r="AL225" t="n">
-        <v>-65.6419438583979</v>
+        <v>-65.1115469159164</v>
       </c>
       <c r="AM225" t="n">
-        <v>1999.787979375</v>
+        <v>1998.43073775</v>
       </c>
       <c r="AN225" t="n">
         <v>209.770270872594</v>
@@ -36145,10 +36145,10 @@
         <v>0.1953</v>
       </c>
       <c r="AX225" t="n">
-        <v>1684.49576617464</v>
+        <v>1683.68816990203</v>
       </c>
       <c r="AY225" t="n">
-        <v>290.93107727987</v>
+        <v>286.067812714089</v>
       </c>
     </row>
     <row r="226">
@@ -36180,10 +36180,10 @@
         <v>0.00567994383495618</v>
       </c>
       <c r="J226" t="n">
-        <v>31244.7659260657</v>
+        <v>31249.2865957074</v>
       </c>
       <c r="K226" t="n">
-        <v>21305.3622059181</v>
+        <v>21297.7917139361</v>
       </c>
       <c r="L226" t="n">
         <v>1939.65198125428</v>
@@ -36195,25 +36195,25 @@
         <v>75.203</v>
       </c>
       <c r="O226" t="n">
-        <v>3321.25788542879</v>
+        <v>3323.03714941431</v>
       </c>
       <c r="P226" t="n">
-        <v>4767.14761837742</v>
+        <v>4748.89002026964</v>
       </c>
       <c r="Q226" t="n">
-        <v>2641.73325967196</v>
+        <v>2647.41045691293</v>
       </c>
       <c r="R226" t="n">
-        <v>554.393164581683</v>
+        <v>557.405226164991</v>
       </c>
       <c r="S226" t="n">
         <v>134.709036355557</v>
       </c>
       <c r="T226" t="n">
-        <v>163.948034350578</v>
+        <v>159.746384540398</v>
       </c>
       <c r="U226" t="n">
-        <v>2263.55853501175</v>
+        <v>2262.0429159531</v>
       </c>
       <c r="V226" t="n">
         <v>241.657946376297</v>
@@ -36249,25 +36249,25 @@
         <v>0</v>
       </c>
       <c r="AG226" t="n">
-        <v>1942.52664111013</v>
+        <v>1940.11104940795</v>
       </c>
       <c r="AH226" t="n">
-        <v>336.507446427527</v>
+        <v>330.233223655259</v>
       </c>
       <c r="AI226" t="n">
-        <v>-2761.57292706633</v>
+        <v>-2754.09443213305</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-1538.18348216172</v>
+        <v>-1540.76594106634</v>
       </c>
       <c r="AK226" t="n">
-        <v>-201.49643441781</v>
+        <v>-202.085451306483</v>
       </c>
       <c r="AL226" t="n">
-        <v>-65.8168783367505</v>
+        <v>-65.1464264005963</v>
       </c>
       <c r="AM226" t="n">
-        <v>2010.48946115889</v>
+        <v>2009.13051565195</v>
       </c>
       <c r="AN226" t="n">
         <v>212.83677314008</v>
@@ -36300,10 +36300,10 @@
         <v>0.171675</v>
       </c>
       <c r="AX226" t="n">
-        <v>1710.15694901122</v>
+        <v>1709.03903152507</v>
       </c>
       <c r="AY226" t="n">
-        <v>295.911003321376</v>
+        <v>290.498217984178</v>
       </c>
     </row>
     <row r="227">
@@ -36335,10 +36335,10 @@
         <v>0.0056310426470525</v>
       </c>
       <c r="J227" t="n">
-        <v>31547.2748645078</v>
+        <v>31551.8393028554</v>
       </c>
       <c r="K227" t="n">
-        <v>21500.7045234993</v>
+        <v>21493.0646200033</v>
       </c>
       <c r="L227" t="n">
         <v>1950.11389145069</v>
@@ -36350,25 +36350,25 @@
         <v>75.203</v>
       </c>
       <c r="O227" t="n">
-        <v>3350.61647652938</v>
+        <v>3352.41146849676</v>
       </c>
       <c r="P227" t="n">
-        <v>4799.87138609857</v>
+        <v>4781.51846726159</v>
       </c>
       <c r="Q227" t="n">
-        <v>2667.21316119132</v>
+        <v>2672.95529418497</v>
       </c>
       <c r="R227" t="n">
-        <v>550.967638791707</v>
+        <v>553.961089224493</v>
       </c>
       <c r="S227" t="n">
         <v>155.206844624839</v>
       </c>
       <c r="T227" t="n">
-        <v>164.27175586129</v>
+        <v>160.061809736797</v>
       </c>
       <c r="U227" t="n">
-        <v>2269.53053501175</v>
+        <v>2268.0149159531</v>
       </c>
       <c r="V227" t="n">
         <v>245.190594913367</v>
@@ -36404,25 +36404,25 @@
         <v>0</v>
       </c>
       <c r="AG227" t="n">
-        <v>1971.37758953044</v>
+        <v>1968.60866854917</v>
       </c>
       <c r="AH227" t="n">
-        <v>341.298888275819</v>
+        <v>334.391675708555</v>
       </c>
       <c r="AI227" t="n">
-        <v>-2793.61028335515</v>
+        <v>-2784.98379878007</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-1554.87482441518</v>
+        <v>-1557.80992480927</v>
       </c>
       <c r="AK227" t="n">
-        <v>-205.5486890442</v>
+        <v>-206.237487613967</v>
       </c>
       <c r="AL227" t="n">
-        <v>-65.8792701987935</v>
+        <v>-65.0684867251562</v>
       </c>
       <c r="AM227" t="n">
-        <v>2021.02714294279</v>
+        <v>2019.66649355389</v>
       </c>
       <c r="AN227" t="n">
         <v>215.94810271373</v>
@@ -36455,10 +36455,10 @@
         <v>0.14805</v>
       </c>
       <c r="AX227" t="n">
-        <v>1735.90619362819</v>
+        <v>1734.40224507345</v>
       </c>
       <c r="AY227" t="n">
-        <v>300.524353916754</v>
+        <v>294.628393717</v>
       </c>
     </row>
     <row r="228">
@@ -36490,10 +36490,10 @@
         <v>0.00558696597638098</v>
       </c>
       <c r="J228" t="n">
-        <v>31843.1726804541</v>
+        <v>31847.7799309731</v>
       </c>
       <c r="K228" t="n">
-        <v>21671.4533838311</v>
+        <v>21663.7528076807</v>
       </c>
       <c r="L228" t="n">
         <v>1961.32746011336</v>
@@ -36505,25 +36505,25 @@
         <v>75.203</v>
       </c>
       <c r="O228" t="n">
-        <v>3380.52824547736</v>
+        <v>3382.339261775</v>
       </c>
       <c r="P228" t="n">
-        <v>4832.96643578863</v>
+        <v>4814.51772724724</v>
       </c>
       <c r="Q228" t="n">
-        <v>2690.47705353563</v>
+        <v>2696.28700882445</v>
       </c>
       <c r="R228" t="n">
-        <v>547.563278895698</v>
+        <v>550.538233173925</v>
       </c>
       <c r="S228" t="n">
         <v>162.820344255939</v>
       </c>
       <c r="T228" t="n">
-        <v>164.107479273765</v>
+        <v>159.901743219221</v>
       </c>
       <c r="U228" t="n">
-        <v>2277.23053501175</v>
+        <v>2275.7149159531</v>
       </c>
       <c r="V228" t="n">
         <v>248.77488506154</v>
@@ -36559,25 +36559,25 @@
         <v>0</v>
       </c>
       <c r="AG228" t="n">
-        <v>2000.68640958851</v>
+        <v>1997.46614829381</v>
       </c>
       <c r="AH228" t="n">
-        <v>346.129184281796</v>
+        <v>338.660865075149</v>
       </c>
       <c r="AI228" t="n">
-        <v>-2820.14739854715</v>
+        <v>-2810.40252483356</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-1570.57807525913</v>
+        <v>-1573.86973845343</v>
       </c>
       <c r="AK228" t="n">
-        <v>-208.73746500739</v>
+        <v>-209.525428719764</v>
       </c>
       <c r="AL228" t="n">
-        <v>-65.819519507919</v>
+        <v>-64.8685448324636</v>
       </c>
       <c r="AM228" t="n">
-        <v>2031.78982472668</v>
+        <v>2030.42747145584</v>
       </c>
       <c r="AN228" t="n">
         <v>219.104914896297</v>
@@ -36610,10 +36610,10 @@
         <v>0.124425</v>
       </c>
       <c r="AX228" t="n">
-        <v>1761.47917793756</v>
+        <v>1759.45981382408</v>
       </c>
       <c r="AY228" t="n">
-        <v>305.012476573248</v>
+        <v>298.755526125317</v>
       </c>
     </row>
     <row r="229">
@@ -36645,10 +36645,10 @@
         <v>0.00554760795794795</v>
       </c>
       <c r="J229" t="n">
-        <v>32140.5730242403</v>
+        <v>32145.223304325</v>
       </c>
       <c r="K229" t="n">
-        <v>21864.8884537073</v>
+        <v>21857.1191437503</v>
       </c>
       <c r="L229" t="n">
         <v>1971.34153426591</v>
@@ -36660,25 +36660,25 @@
         <v>75.203</v>
       </c>
       <c r="O229" t="n">
-        <v>3409.71913955511</v>
+        <v>3411.54579399599</v>
       </c>
       <c r="P229" t="n">
-        <v>4866.43518654803</v>
+        <v>4847.89021605588</v>
       </c>
       <c r="Q229" t="n">
-        <v>2715.66964953021</v>
+        <v>2721.54351794672</v>
       </c>
       <c r="R229" t="n">
-        <v>544.179954112255</v>
+        <v>547.13652652134</v>
       </c>
       <c r="S229" t="n">
         <v>160.445027356869</v>
       </c>
       <c r="T229" t="n">
-        <v>164.305577511663</v>
+        <v>160.094764608062</v>
       </c>
       <c r="U229" t="n">
-        <v>2284.93053501175</v>
+        <v>2283.4149159531</v>
       </c>
       <c r="V229" t="n">
         <v>252.41157173769</v>
@@ -36714,25 +36714,25 @@
         <v>0</v>
       </c>
       <c r="AG229" t="n">
-        <v>2030.48566595013</v>
+        <v>2027.48759529629</v>
       </c>
       <c r="AH229" t="n">
-        <v>351.381644717384</v>
+        <v>343.863348488739</v>
       </c>
       <c r="AI229" t="n">
-        <v>-2845.21533776699</v>
+        <v>-2834.39424272457</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-1585.48364353128</v>
+        <v>-1588.88964295594</v>
       </c>
       <c r="AK229" t="n">
-        <v>-211.383463477799</v>
+        <v>-212.269979603809</v>
       </c>
       <c r="AL229" t="n">
-        <v>-65.7330387583077</v>
+        <v>-64.6417036527323</v>
       </c>
       <c r="AM229" t="n">
-        <v>2046.43128151058</v>
+        <v>2045.06722435779</v>
       </c>
       <c r="AN229" t="n">
         <v>222.307874570001</v>
@@ -36765,10 +36765,10 @@
         <v>0.1008</v>
       </c>
       <c r="AX229" t="n">
-        <v>1787.64216889032</v>
+        <v>1785.07652884812</v>
       </c>
       <c r="AY229" t="n">
-        <v>309.446361833068</v>
+        <v>303.108550408733</v>
       </c>
     </row>
     <row r="230">
@@ -36800,10 +36800,10 @@
         <v>0.00550459474437348</v>
       </c>
       <c r="J230" t="n">
-        <v>32445.5861757489</v>
+        <v>32450.2805868633</v>
       </c>
       <c r="K230" t="n">
-        <v>22070.6704429373</v>
+        <v>22062.8280119094</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -36875,19 +36875,19 @@
         <v>0</v>
       </c>
       <c r="AI230" t="n">
-        <v>-2280.50678452323</v>
+        <v>-2271.8308873708</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-1272.1300716309</v>
+        <v>-1274.86472678524</v>
       </c>
       <c r="AK230" t="n">
-        <v>-196.053463477799</v>
+        <v>-196.939979603809</v>
       </c>
       <c r="AL230" t="n">
-        <v>-60.0530387583078</v>
+        <v>-58.9617036527323</v>
       </c>
       <c r="AM230" t="n">
-        <v>1537.13061113293</v>
+        <v>1536.10756826834</v>
       </c>
       <c r="AN230" t="n">
         <v>167.934836635334</v>
@@ -36920,10 +36920,10 @@
         <v>0.0819</v>
       </c>
       <c r="AX230" t="n">
-        <v>1350.57367464054</v>
+        <v>1348.55154273134</v>
       </c>
       <c r="AY230" t="n">
-        <v>233.732186386875</v>
+        <v>228.8060750863</v>
       </c>
     </row>
     <row r="231">
@@ -36955,10 +36955,10 @@
         <v>0.00545389484594594</v>
       </c>
       <c r="J231" t="n">
-        <v>32742.4856769218</v>
+        <v>32747.2230451371</v>
       </c>
       <c r="K231" t="n">
-        <v>22254.2681299138</v>
+        <v>22246.3604606231</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -37030,19 +37030,19 @@
         <v>0</v>
       </c>
       <c r="AI231" t="n">
-        <v>-1712.40799982648</v>
+        <v>-1705.88841333007</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-955.375984736884</v>
+        <v>-957.430527031876</v>
       </c>
       <c r="AK231" t="n">
-        <v>-179.606796811132</v>
+        <v>-180.493312937142</v>
       </c>
       <c r="AL231" t="n">
-        <v>-54.5863720916411</v>
+        <v>-53.4950369860657</v>
       </c>
       <c r="AM231" t="n">
-        <v>1026.48624075529</v>
+        <v>1025.80421217889</v>
       </c>
       <c r="AN231" t="n">
         <v>112.766952779827</v>
@@ -37075,10 +37075,10 @@
         <v>0.063</v>
       </c>
       <c r="AX231" t="n">
-        <v>907.013716996196</v>
+        <v>905.614592307771</v>
       </c>
       <c r="AY231" t="n">
-        <v>156.939936524816</v>
+        <v>153.567948051875</v>
       </c>
     </row>
     <row r="232">
@@ -37110,10 +37110,10 @@
         <v>0.00542022049047874</v>
       </c>
       <c r="J232" t="n">
-        <v>33042.9912449106</v>
+        <v>33047.7720919729</v>
       </c>
       <c r="K232" t="n">
-        <v>22438.367724181</v>
+        <v>22430.3946382835</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37185,19 +37185,19 @@
         <v>0</v>
       </c>
       <c r="AI232" t="n">
-        <v>-1434.90044765176</v>
+        <v>-1429.42983527443</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-799.939824525247</v>
+        <v>-801.66242823141</v>
       </c>
       <c r="AK232" t="n">
-        <v>-163.170130144465</v>
+        <v>-164.056646270475</v>
       </c>
       <c r="AL232" t="n">
-        <v>-49.1663720916411</v>
+        <v>-48.0750369860657</v>
       </c>
       <c r="AM232" t="n">
-        <v>514.109370377644</v>
+        <v>513.768356089447</v>
       </c>
       <c r="AN232" t="n">
         <v>56.7926036409802</v>
@@ -37230,10 +37230,10 @@
         <v>0.0441</v>
       </c>
       <c r="AX232" t="n">
-        <v>456.85927483878</v>
+        <v>456.184708941665</v>
       </c>
       <c r="AY232" t="n">
-        <v>79.0608700614115</v>
+        <v>77.3692534099663</v>
       </c>
     </row>
     <row r="233">
@@ -37265,10 +37265,10 @@
         <v>0.00537879404345354</v>
       </c>
       <c r="J233" t="n">
-        <v>33354.2148448243</v>
+        <v>33359.0407214792</v>
       </c>
       <c r="K233" t="n">
-        <v>22635.7176709255</v>
+        <v>22627.6744601376</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -37340,16 +37340,16 @@
         <v>0</v>
       </c>
       <c r="AI233" t="n">
-        <v>-1155.98523760876</v>
+        <v>-1151.56898585006</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-642.905587435747</v>
+        <v>-644.291776672145</v>
       </c>
       <c r="AK233" t="n">
-        <v>-146.192371639187</v>
+        <v>-146.986646270475</v>
       </c>
       <c r="AL233" t="n">
-        <v>-43.7222137699462</v>
+        <v>-42.6017036527323</v>
       </c>
       <c r="AM233" t="n">
         <v>0</v>
@@ -37420,10 +37420,10 @@
         <v>0.00534192357811758</v>
       </c>
       <c r="J234" t="n">
-        <v>33668.0428263273</v>
+        <v>33672.9141093914</v>
       </c>
       <c r="K234" t="n">
-        <v>22843.105763486</v>
+        <v>22834.9888609263</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -37495,16 +37495,16 @@
         <v>0</v>
       </c>
       <c r="AI234" t="n">
-        <v>-869.956380506113</v>
+        <v>-866.635584633883</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-484.40159185543</v>
+        <v>-485.447149257369</v>
       </c>
       <c r="AK234" t="n">
-        <v>-128.655708658236</v>
+        <v>-129.354705222913</v>
       </c>
       <c r="AL234" t="n">
-        <v>-38.2635604552343</v>
+        <v>-37.2829443584303</v>
       </c>
       <c r="AM234" t="n">
         <v>0</v>
@@ -37575,10 +37575,10 @@
         <v>0.00532158987529296</v>
       </c>
       <c r="J235" t="n">
-        <v>33974.2580001079</v>
+        <v>33979.1735881171</v>
       </c>
       <c r="K235" t="n">
-        <v>23048.0847010507</v>
+        <v>23039.8949627707</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -37650,16 +37650,16 @@
         <v>0</v>
       </c>
       <c r="AI235" t="n">
-        <v>-581.964097340199</v>
+        <v>-579.744476598187</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-324.36880218395</v>
+        <v>-325.06983160627</v>
       </c>
       <c r="AK235" t="n">
-        <v>-110.54174217604</v>
+        <v>-111.142324138864</v>
       </c>
       <c r="AL235" t="n">
-        <v>-32.8071619172139</v>
+        <v>-31.966382055546</v>
       </c>
       <c r="AM235" t="n">
         <v>0</v>
@@ -37730,10 +37730,10 @@
         <v>0.00528941636235492</v>
       </c>
       <c r="J236" t="n">
-        <v>34289.2880038828</v>
+        <v>34294.2491722167</v>
       </c>
       <c r="K236" t="n">
-        <v>23264.1055990132</v>
+        <v>23255.8391014431</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -37805,16 +37805,16 @@
         <v>0</v>
       </c>
       <c r="AI236" t="n">
-        <v>-291.986111192882</v>
+        <v>-290.873412963353</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-162.940178971813</v>
+        <v>-163.292611076803</v>
       </c>
       <c r="AK236" t="n">
-        <v>-91.8314674747158</v>
+        <v>-92.3303950463213</v>
       </c>
       <c r="AL236" t="n">
-        <v>-27.3460927703325</v>
+        <v>-26.6452688418678</v>
       </c>
       <c r="AM236" t="n">
         <v>0</v>
@@ -37885,10 +37885,10 @@
         <v>0.00524963654830413</v>
       </c>
       <c r="J237" t="n">
-        <v>34611.6303098121</v>
+        <v>34616.6381164559</v>
       </c>
       <c r="K237" t="n">
-        <v>23484.0413738439</v>
+        <v>23475.6967259</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -37966,10 +37966,10 @@
         <v>0</v>
       </c>
       <c r="AK237" t="n">
-        <v>-73.2368012127114</v>
+        <v>-73.6347025028249</v>
       </c>
       <c r="AL237" t="n">
-        <v>-21.8877615665765</v>
+        <v>-21.3268234034826</v>
       </c>
       <c r="AM237" t="n">
         <v>0</v>
@@ -38040,10 +38040,10 @@
         <v>0.00521033508596069</v>
       </c>
       <c r="J238" t="n">
-        <v>34939.4818844878</v>
+        <v>34944.5371265538</v>
       </c>
       <c r="K238" t="n">
-        <v>23713.9149130325</v>
+        <v>23705.4885835022</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -38121,10 +38121,10 @@
         <v>0</v>
       </c>
       <c r="AK238" t="n">
-        <v>-54.7570290599886</v>
+        <v>-55.0545282973252</v>
       </c>
       <c r="AL238" t="n">
-        <v>-16.4228270882239</v>
+        <v>-16.0019439188027</v>
       </c>
       <c r="AM238" t="n">
         <v>0</v>
@@ -38195,10 +38195,10 @@
         <v>0.00516756143130825</v>
       </c>
       <c r="J239" t="n">
-        <v>35270.4386833661</v>
+        <v>35275.5418101356</v>
       </c>
       <c r="K239" t="n">
-        <v>23949.30943242</v>
+        <v>23940.7994595184</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AK239" t="n">
-        <v>-36.3914411002651</v>
+        <v>-36.5891586565088</v>
       </c>
       <c r="AL239" t="n">
-        <v>-10.9471018928476</v>
+        <v>-10.6665502609094</v>
       </c>
       <c r="AM239" t="n">
         <v>0</v>
@@ -38350,10 +38350,10 @@
         <v>0.00510570215168871</v>
       </c>
       <c r="J240" t="n">
-        <v>35603.2986841751</v>
+        <v>35608.4499710141</v>
       </c>
       <c r="K240" t="n">
-        <v>24181.7928895208</v>
+        <v>24173.2003076435</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -38431,10 +38431,10 @@
         <v>0</v>
       </c>
       <c r="AK240" t="n">
-        <v>-18.1393318037418</v>
+        <v>-18.237884217378</v>
       </c>
       <c r="AL240" t="n">
-        <v>-5.4768525837221</v>
+        <v>-5.33649215360207</v>
       </c>
       <c r="AM240" t="n">
         <v>0</v>
@@ -38505,10 +38505,10 @@
         <v>0.00504465278509314</v>
       </c>
       <c r="J241" t="n">
-        <v>35938.6628980505</v>
+        <v>35943.8627072829</v>
       </c>
       <c r="K241" t="n">
-        <v>24417.0870274501</v>
+        <v>24408.4108378704</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -38660,10 +38660,10 @@
         <v>0.00499215850685553</v>
       </c>
       <c r="J242" t="n">
-        <v>36280.7384029444</v>
+        <v>36285.9877055977</v>
       </c>
       <c r="K242" t="n">
-        <v>24661.1143522394</v>
+        <v>24652.3514517703</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -38815,10 +38815,10 @@
         <v>0.00493645950017374</v>
       </c>
       <c r="J243" t="n">
-        <v>36629.4250303341</v>
+        <v>36634.7247829428</v>
       </c>
       <c r="K243" t="n">
-        <v>24919.1950811713</v>
+        <v>24910.3404761787</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -38970,10 +38970,10 @@
         <v>0.00488530487992378</v>
       </c>
       <c r="J244" t="n">
-        <v>36971.500535228</v>
+        <v>36976.8497812576</v>
       </c>
       <c r="K244" t="n">
-        <v>25174.8666551073</v>
+        <v>25165.9212016427</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -39125,10 +39125,10 @@
         <v>0.00484625476688616</v>
       </c>
       <c r="J245" t="n">
-        <v>37321.2890163669</v>
+        <v>37326.6888717745</v>
       </c>
       <c r="K245" t="n">
-        <v>25437.3641681983</v>
+        <v>25428.3254407823</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -39280,10 +39280,10 @@
         <v>0.0048076557063792</v>
       </c>
       <c r="J246" t="n">
-        <v>37674.8839013671</v>
+        <v>37680.3349168846</v>
       </c>
       <c r="K246" t="n">
-        <v>25700.6647329545</v>
+        <v>25691.5324462367</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -39435,10 +39435,10 @@
         <v>0.00478086441968562</v>
       </c>
       <c r="J247" t="n">
-        <v>38032.5856957964</v>
+        <v>38038.0884656349</v>
       </c>
       <c r="K247" t="n">
-        <v>25970.5904739494</v>
+        <v>25961.3622737879</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -39590,10 +39590,10 @@
         <v>0.00473926501804089</v>
       </c>
       <c r="J248" t="n">
-        <v>38394.4945681775</v>
+        <v>38400.0497010408</v>
       </c>
       <c r="K248" t="n">
-        <v>26240.4158334861</v>
+        <v>26231.0917555497</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -39745,10 +39745,10 @@
         <v>0.00471315781573667</v>
       </c>
       <c r="J249" t="n">
-        <v>38760.6105185105</v>
+        <v>38766.2186231024</v>
       </c>
       <c r="K249" t="n">
-        <v>26512.248822186</v>
+        <v>26502.8281530985</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -39900,10 +39900,10 @@
         <v>0.00467984343253258</v>
       </c>
       <c r="J250" t="n">
-        <v>39130.3325356594</v>
+        <v>39135.9941337261</v>
       </c>
       <c r="K250" t="n">
-        <v>26786.6917287981</v>
+        <v>26777.1735411702</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -40055,10 +40055,10 @@
         <v>0.0046431744591946</v>
       </c>
       <c r="J251" t="n">
-        <v>39503.3601140561</v>
+        <v>39509.075683865</v>
       </c>
       <c r="K251" t="n">
-        <v>27064.4472235295</v>
+        <v>27054.8303402904</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -40210,10 +40210,10 @@
         <v>0.00460321336856051</v>
       </c>
       <c r="J252" t="n">
-        <v>39880.0939277914</v>
+        <v>39885.8640055815</v>
       </c>
       <c r="K252" t="n">
-        <v>27345.3145434639</v>
+        <v>27335.5978588803</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -40365,10 +40365,10 @@
         <v>0.00457107075767049</v>
       </c>
       <c r="J253" t="n">
-        <v>40260.2334712972</v>
+        <v>40266.0585498288</v>
       </c>
       <c r="K253" t="n">
-        <v>27629.3940700595</v>
+        <v>27619.5764427292</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -40520,10 +40520,10 @@
         <v>0.00449893851450689</v>
       </c>
       <c r="J254" t="n">
-        <v>40641.3747000297</v>
+        <v>40647.2549242322</v>
       </c>
       <c r="K254" t="n">
-        <v>27915.7823701928</v>
+        <v>27905.8629797332</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -40675,10 +40675,10 @@
         <v>0.00453719183232471</v>
       </c>
       <c r="J255" t="n">
-        <v>41027.7246919406</v>
+        <v>41033.6608154475</v>
       </c>
       <c r="K255" t="n">
-        <v>28207.4908876085</v>
+        <v>28197.4678435724</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -40830,10 +40830,10 @@
         <v>0.00452033241158278</v>
       </c>
       <c r="J256" t="n">
-        <v>41416.8794024861</v>
+        <v>41422.8718310999</v>
       </c>
       <c r="K256" t="n">
-        <v>28502.6123746018</v>
+        <v>28492.4844642494</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -40985,10 +40985,10 @@
         <v>0.00449275624446099</v>
       </c>
       <c r="J257" t="n">
-        <v>41808.3379890528</v>
+        <v>41814.3870561113</v>
       </c>
       <c r="K257" t="n">
-        <v>28799.8418722165</v>
+        <v>28789.6083465027</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -41140,10 +41140,10 @@
         <v>0.00446545931210318</v>
       </c>
       <c r="J258" t="n">
-        <v>42202.2006201634</v>
+        <v>42208.3066734975</v>
       </c>
       <c r="K258" t="n">
-        <v>29098.9786175362</v>
+        <v>29088.6387987536</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -41295,10 +41295,10 @@
         <v>0.00443843729721394</v>
       </c>
       <c r="J259" t="n">
-        <v>42598.6676328633</v>
+        <v>42604.8310492895</v>
       </c>
       <c r="K259" t="n">
-        <v>29400.7252807681</v>
+        <v>29390.2782415274</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -41450,10 +41450,10 @@
         <v>0.00440811664554808</v>
       </c>
       <c r="J260" t="n">
-        <v>42997.839195675</v>
+        <v>43004.0603665031</v>
       </c>
       <c r="K260" t="n">
-        <v>29706.1860579519</v>
+        <v>29695.6304785071</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
